--- a/assets/AcrossTheWall.xlsx
+++ b/assets/AcrossTheWall.xlsx
@@ -10,7 +10,7 @@
     <sheet name="AcrossTheWall" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">AcrossTheWall!$A$1:$O$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">AcrossTheWall!$A$1:$P$20</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="77">
   <si>
     <t>question-room</t>
   </si>
@@ -62,6 +62,9 @@
     <t>answer-length</t>
   </si>
   <si>
+    <t>order-check</t>
+  </si>
+  <si>
     <t>correct-answer</t>
   </si>
   <si>
@@ -84,6 +87,9 @@
   </si>
   <si>
     <t>number</t>
+  </si>
+  <si>
+    <t>Y</t>
   </si>
   <si>
     <t>Z</t>
@@ -202,98 +208,21 @@
     <t>Decrypt the message below</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>. . . .</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">   </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>. -</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">   </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>. - - .</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">   </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>. - - .</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">   </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>- . - -</t>
-    </r>
+    <t>. . . .    . -    . - - .   . - - .   - . - -</t>
+  </si>
+  <si>
+    <t>HAPPY</t>
+  </si>
+  <si>
+    <t>Decode the following caesar cipher</t>
+  </si>
+  <si>
+    <t>KHOOR</t>
   </si>
   <si>
     <t>HELLO</t>
   </si>
   <si>
-    <t>Decode the following caesar cipher</t>
-  </si>
-  <si>
-    <t>KHOOR</t>
-  </si>
-  <si>
     <t>This is an incomplete copy of a number pattern. Find the original and determine "?" value.</t>
   </si>
   <si>
@@ -361,6 +290,9 @@
   </si>
   <si>
     <t>coordinates</t>
+  </si>
+  <si>
+    <t>N</t>
   </si>
   <si>
     <t>B2,C2,C4</t>
@@ -1575,7 +1507,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O20"/>
+  <dimension ref="A1:P20"/>
   <sheetFormatPr defaultColWidth="9.81818181818182" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="13.8818181818182" customWidth="1"/>
@@ -1585,11 +1517,11 @@
     <col min="6" max="7" width="20.4545454545455" customWidth="1"/>
     <col min="8" max="8" width="12.9727272727273" customWidth="1"/>
     <col min="9" max="9" width="12.3090909090909" customWidth="1"/>
-    <col min="10" max="10" width="15.2818181818182" customWidth="1"/>
-    <col min="11" max="14" width="20.4545454545455" customWidth="1"/>
+    <col min="10" max="11" width="15.2818181818182" customWidth="1"/>
+    <col min="12" max="15" width="20.4545454545455" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:16">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1635,563 +1567,602 @@
       <c r="O1" s="1" t="s">
         <v>14</v>
       </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
     </row>
-    <row r="2" spans="1:15">
+    <row r="2" spans="1:16">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B2">
         <v>100</v>
       </c>
       <c r="C2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J2">
         <v>4</v>
       </c>
-      <c r="K2">
+      <c r="K2" t="s">
+        <v>19</v>
+      </c>
+      <c r="L2">
         <v>7249</v>
       </c>
     </row>
-    <row r="3" ht="29" spans="1:15">
+    <row r="3" ht="29" spans="1:16">
       <c r="A3" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B3">
         <v>100</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E3" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J3">
         <v>2</v>
       </c>
-      <c r="K3">
+      <c r="K3" t="s">
+        <v>19</v>
+      </c>
+      <c r="L3">
         <v>25</v>
       </c>
     </row>
-    <row r="4" spans="1:15">
+    <row r="4" spans="1:16">
       <c r="A4" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B4">
         <v>100</v>
       </c>
       <c r="C4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D4" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J4">
         <v>4</v>
       </c>
-      <c r="K4">
+      <c r="K4" t="s">
+        <v>19</v>
+      </c>
+      <c r="L4">
         <v>3852</v>
       </c>
     </row>
-    <row r="5" ht="29" spans="1:15">
+    <row r="5" ht="29" spans="1:16">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B5">
         <v>100</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D5" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E5" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F5" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G5" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="J5">
         <v>1</v>
       </c>
-      <c r="K5" s="3" t="s">
-        <v>29</v>
+      <c r="L5" s="3" t="s">
+        <v>31</v>
       </c>
     </row>
-    <row r="6" ht="16.5" spans="1:15">
+    <row r="6" ht="16.5" spans="1:16">
       <c r="A6" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B6">
         <v>100</v>
       </c>
       <c r="C6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E6" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J6">
         <v>2</v>
       </c>
-      <c r="K6">
+      <c r="K6" t="s">
+        <v>19</v>
+      </c>
+      <c r="L6">
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:15">
+    <row r="7" spans="1:16">
       <c r="A7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B7">
         <v>100</v>
       </c>
       <c r="C7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D7" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E7" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J7">
         <v>4</v>
       </c>
-      <c r="K7">
+      <c r="K7" t="s">
+        <v>19</v>
+      </c>
+      <c r="L7">
         <v>1738</v>
       </c>
     </row>
-    <row r="8" spans="1:15">
+    <row r="8" spans="1:16">
       <c r="A8" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B8">
         <v>100</v>
       </c>
       <c r="C8" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G8" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I8" s="7" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J8">
         <v>2</v>
       </c>
-      <c r="K8">
+      <c r="K8" t="s">
+        <v>19</v>
+      </c>
+      <c r="L8">
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:15">
+    <row r="9" spans="1:16">
       <c r="A9" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B9">
         <v>100</v>
       </c>
       <c r="C9" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D9" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E9" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F9" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G9" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="J9">
         <v>4</v>
       </c>
       <c r="K9" t="s">
-        <v>37</v>
+        <v>19</v>
+      </c>
+      <c r="L9" t="s">
+        <v>39</v>
       </c>
     </row>
-    <row r="10" spans="1:15">
+    <row r="10" spans="1:16">
       <c r="A10" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B10">
         <v>100</v>
       </c>
       <c r="C10" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E10" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F10" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G10" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="J10">
         <v>1</v>
       </c>
-      <c r="K10" t="s">
-        <v>40</v>
+      <c r="L10" t="s">
+        <v>42</v>
       </c>
     </row>
-    <row r="11" spans="1:15">
+    <row r="11" spans="1:16">
       <c r="A11" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B11">
         <v>100</v>
       </c>
       <c r="C11" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D11" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E11" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F11" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G11" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="J11">
         <v>1</v>
       </c>
-      <c r="K11" t="s">
-        <v>40</v>
+      <c r="L11" t="s">
+        <v>45</v>
       </c>
     </row>
-    <row r="12" spans="1:15">
+    <row r="12" spans="1:16">
       <c r="A12" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B12">
         <v>100</v>
       </c>
       <c r="C12" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D12" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="E12" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F12" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G12" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J12">
         <v>2</v>
       </c>
-      <c r="K12">
+      <c r="K12" t="s">
+        <v>19</v>
+      </c>
+      <c r="L12">
         <v>32</v>
       </c>
     </row>
-    <row r="13" spans="1:15">
+    <row r="13" spans="1:16">
       <c r="A13" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B13">
         <v>100</v>
       </c>
       <c r="C13" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D13" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E13" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F13" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G13" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="J13">
         <v>1</v>
       </c>
-      <c r="K13" t="s">
-        <v>46</v>
+      <c r="L13" t="s">
+        <v>49</v>
       </c>
     </row>
-    <row r="14" spans="1:15">
+    <row r="14" spans="1:16">
       <c r="A14" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B14">
         <v>100</v>
       </c>
       <c r="C14" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="D14" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="E14" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F14" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J14">
         <v>2</v>
       </c>
-      <c r="K14">
+      <c r="K14" t="s">
+        <v>19</v>
+      </c>
+      <c r="L14">
         <v>20</v>
       </c>
     </row>
-    <row r="15" spans="1:15">
+    <row r="15" spans="1:16">
       <c r="A15" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B15">
         <v>100</v>
       </c>
       <c r="C15" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="D15" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="E15" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F15" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G15" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J15">
         <v>2</v>
       </c>
-      <c r="K15">
+      <c r="K15" t="s">
+        <v>19</v>
+      </c>
+      <c r="L15">
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="1:15">
+    <row r="16" spans="1:16">
       <c r="A16" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B16">
         <v>300</v>
       </c>
       <c r="C16" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="D16" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E16" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="F16" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G16" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="J16">
         <v>4</v>
       </c>
       <c r="K16" t="s">
-        <v>53</v>
+        <v>19</v>
+      </c>
+      <c r="L16" t="s">
+        <v>56</v>
       </c>
     </row>
-    <row r="17" spans="1:15">
+    <row r="17" spans="1:16">
       <c r="A17" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B17">
         <v>300</v>
       </c>
       <c r="C17" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="F17" t="s">
+        <v>58</v>
+      </c>
+      <c r="G17" t="s">
         <v>55</v>
       </c>
-      <c r="G17" t="s">
-        <v>52</v>
-      </c>
-      <c r="K17" t="s">
-        <v>13</v>
-      </c>
       <c r="L17" t="s">
-        <v>56</v>
+        <v>14</v>
       </c>
       <c r="M17" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="N17" t="s">
-        <v>58</v>
+        <v>60</v>
+      </c>
+      <c r="O17" t="s">
+        <v>61</v>
       </c>
     </row>
-    <row r="18" spans="1:15">
+    <row r="18" spans="1:16">
       <c r="A18" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B18">
         <v>300</v>
       </c>
       <c r="C18" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F18" t="s">
+        <v>58</v>
+      </c>
+      <c r="G18" t="s">
         <v>55</v>
       </c>
-      <c r="G18" t="s">
-        <v>52</v>
-      </c>
-      <c r="K18" t="s">
-        <v>11</v>
-      </c>
       <c r="L18" t="s">
-        <v>60</v>
+        <v>12</v>
       </c>
       <c r="M18" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="N18" t="s">
-        <v>62</v>
+        <v>64</v>
+      </c>
+      <c r="O18" t="s">
+        <v>65</v>
       </c>
     </row>
-    <row r="19" spans="1:15">
+    <row r="19" spans="1:16">
       <c r="A19" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B19">
         <v>300</v>
       </c>
       <c r="C19" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="D19" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="E19" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="F19" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G19" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="J19">
         <v>3</v>
       </c>
       <c r="K19" t="s">
-        <v>66</v>
+        <v>69</v>
+      </c>
+      <c r="L19" t="s">
+        <v>70</v>
       </c>
     </row>
-    <row r="20" spans="1:15">
+    <row r="20" spans="1:16">
       <c r="A20" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B20">
         <v>300</v>
       </c>
       <c r="C20" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="D20" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="E20" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="F20" t="s">
+        <v>58</v>
+      </c>
+      <c r="G20" t="s">
         <v>55</v>
       </c>
-      <c r="G20" t="s">
-        <v>52</v>
-      </c>
-      <c r="K20" t="s">
-        <v>12</v>
-      </c>
       <c r="L20" t="s">
-        <v>69</v>
+        <v>13</v>
       </c>
       <c r="M20" t="s">
-        <v>70</v>
-      </c>
-      <c r="N20" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="O20" t="s">
-        <v>72</v>
+        <v>73</v>
+      </c>
+      <c r="N20" t="s">
+        <v>74</v>
+      </c>
+      <c r="O20" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="P20" t="s">
+        <v>76</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:O20" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:P20" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/assets/AcrossTheWall.xlsx
+++ b/assets/AcrossTheWall.xlsx
@@ -199,10 +199,10 @@
     <t>Determine the seating arrangement for</t>
   </si>
   <si>
-    <t>Alice,Bob,Charlie,David</t>
-  </si>
-  <si>
-    <t>Alice,David,Bob,Charlie</t>
+    <t>Angela,Krystal,Ray,Johnny</t>
+  </si>
+  <si>
+    <t>Angela,Johnny,Krystal,Ray</t>
   </si>
   <si>
     <t>Decrypt the message below</t>
@@ -229,10 +229,10 @@
     <t>2, ■, ■, 16, ?</t>
   </si>
   <si>
-    <t>. . .   - - -   . . . .</t>
-  </si>
-  <si>
-    <t>SOH</t>
+    <t>. . .   - - -   . - -</t>
+  </si>
+  <si>
+    <t>SOW</t>
   </si>
   <si>
     <t>Solve the below</t>
@@ -253,7 +253,7 @@
     <t>image</t>
   </si>
   <si>
-    <t>Chris,Bob,Anna,David</t>
+    <t>Chris,Samatha,Anna,Jess</t>
   </si>
   <si>
     <t>Three boxes contain either🍍🍇 or🍉. What is in box 3?</t>

--- a/assets/AcrossTheWall.xlsx
+++ b/assets/AcrossTheWall.xlsx
@@ -10,7 +10,7 @@
     <sheet name="AcrossTheWall" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">AcrossTheWall!$A$1:$P$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">AcrossTheWall!$A$1:$P$23</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="83">
   <si>
     <t>question-room</t>
   </si>
@@ -214,7 +214,7 @@
     <t>HAPPY</t>
   </si>
   <si>
-    <t>Decode the following caesar cipher</t>
+    <t>Decode the following caesar cipher sent from Jason</t>
   </si>
   <si>
     <t>KHOOR</t>
@@ -314,6 +314,24 @@
   </si>
   <si>
     <t>DotPatternD</t>
+  </si>
+  <si>
+    <t>An old phone's message has been scrambled into keypad numbers. Decode the following message.</t>
+  </si>
+  <si>
+    <t>22 888 22 22 555 33 0 9 777 2 7</t>
+  </si>
+  <si>
+    <t>BUBBLE WRAP</t>
+  </si>
+  <si>
+    <t>Answer the following caesar cipher sent from Victoria</t>
+  </si>
+  <si>
+    <t>OVD THUF YLK OLHYAZ</t>
+  </si>
+  <si>
+    <t>♪ ♫ ♩</t>
   </si>
 </sst>
 </file>
@@ -1507,7 +1525,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:P20"/>
+  <dimension ref="A1:P23"/>
   <sheetFormatPr defaultColWidth="9.81818181818182" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="13.8818181818182" customWidth="1"/>
@@ -1762,7 +1780,7 @@
         <v>12</v>
       </c>
       <c r="B8">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="C8" t="s">
         <v>35</v>
@@ -1791,7 +1809,7 @@
         <v>20</v>
       </c>
       <c r="B9">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="C9" t="s">
         <v>37</v>
@@ -1852,7 +1870,7 @@
         <v>20</v>
       </c>
       <c r="B11">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="C11" t="s">
         <v>43</v>
@@ -2161,8 +2179,102 @@
         <v>76</v>
       </c>
     </row>
+    <row r="21" spans="1:16">
+      <c r="A21" t="s">
+        <v>12</v>
+      </c>
+      <c r="B21">
+        <v>300</v>
+      </c>
+      <c r="C21" t="s">
+        <v>77</v>
+      </c>
+      <c r="D21" t="s">
+        <v>78</v>
+      </c>
+      <c r="E21" t="s">
+        <v>26</v>
+      </c>
+      <c r="F21" t="s">
+        <v>29</v>
+      </c>
+      <c r="G21" t="s">
+        <v>30</v>
+      </c>
+      <c r="J21">
+        <v>1</v>
+      </c>
+      <c r="K21"/>
+      <c r="L21" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16">
+      <c r="A22" t="s">
+        <v>12</v>
+      </c>
+      <c r="B22">
+        <v>300</v>
+      </c>
+      <c r="C22" t="s">
+        <v>80</v>
+      </c>
+      <c r="D22" t="s">
+        <v>81</v>
+      </c>
+      <c r="E22" t="s">
+        <v>26</v>
+      </c>
+      <c r="F22" t="s">
+        <v>17</v>
+      </c>
+      <c r="G22" t="s">
+        <v>18</v>
+      </c>
+      <c r="J22">
+        <v>2</v>
+      </c>
+      <c r="K22" t="s">
+        <v>19</v>
+      </c>
+      <c r="L22">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16">
+      <c r="A23" t="s">
+        <v>12</v>
+      </c>
+      <c r="B23">
+        <v>100</v>
+      </c>
+      <c r="C23" t="s">
+        <v>16</v>
+      </c>
+      <c r="D23" t="s">
+        <v>82</v>
+      </c>
+      <c r="E23" t="s">
+        <v>26</v>
+      </c>
+      <c r="F23" t="s">
+        <v>17</v>
+      </c>
+      <c r="G23" t="s">
+        <v>18</v>
+      </c>
+      <c r="J23">
+        <v>3</v>
+      </c>
+      <c r="K23" t="s">
+        <v>19</v>
+      </c>
+      <c r="L23">
+        <v>552</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:P20" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:P23" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
